--- a/data/trans_orig/IQ3004_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado</t>
+          <t>Menores según la edad en meses en la que empezaron a comer carne o pescado (tasa de respuesta: 61,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,54</t>
+          <t>6,13; 7,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,89</t>
+          <t>6,89; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 8,2</t>
+          <t>6,87; 8,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 7,99</t>
+          <t>6,49; 7,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,09; 8,45</t>
+          <t>7,15; 8,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,73</t>
+          <t>6,7; 7,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,53</t>
+          <t>6,47; 7,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 8,38</t>
+          <t>7,27; 8,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,81</t>
+          <t>6,94; 7,82</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,67</t>
+          <t>5,06; 6,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,4</t>
+          <t>6,44; 8,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,16</t>
+          <t>7,32; 9,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,07</t>
+          <t>6,5; 8,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,85</t>
+          <t>6,18; 7,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,03</t>
+          <t>6,86; 9,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,46</t>
+          <t>6,15; 7,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,77</t>
+          <t>6,45; 7,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,1</t>
+          <t>7,32; 9,11</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,3</t>
+          <t>7,14; 9,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,39</t>
+          <t>6,61; 8,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 9,62</t>
+          <t>6,52; 9,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,69</t>
+          <t>6,66; 9,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 8,74</t>
+          <t>6,69; 8,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 7,7</t>
+          <t>5,34; 7,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,01</t>
+          <t>7,09; 9,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 8,15</t>
+          <t>6,84; 8,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,52</t>
+          <t>6,4; 8,56</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,08</t>
+          <t>6,26; 7,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 8,16</t>
+          <t>7,02; 8,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,33</t>
+          <t>7,57; 9,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,69</t>
+          <t>6,69; 7,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,97</t>
+          <t>7,15; 8,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,68</t>
+          <t>6,27; 7,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,64</t>
+          <t>6,72; 7,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 8,31</t>
+          <t>7,29; 8,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,31</t>
+          <t>7,15; 8,37</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 8,7</t>
+          <t>6,17; 8,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,05</t>
+          <t>6,56; 8,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 9,94</t>
+          <t>8,04; 9,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,79</t>
+          <t>5,37; 7,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 9,85</t>
+          <t>7,41; 9,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,95</t>
+          <t>6,52; 11,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,72</t>
+          <t>5,93; 7,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,48</t>
+          <t>7,16; 8,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,48</t>
+          <t>7,44; 10,63</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,21</t>
+          <t>6,33; 9,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,29; 18,4</t>
+          <t>8,27; 17,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,18</t>
+          <t>6,27; 9,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,98</t>
+          <t>7,49; 10,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,62</t>
+          <t>7,39; 8,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 7,88</t>
+          <t>6,28; 7,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,21; 9,06</t>
+          <t>7,23; 9,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,44</t>
+          <t>8,08; 13,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,4</t>
+          <t>6,59; 8,26</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,53</t>
+          <t>6,7; 7,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,54</t>
+          <t>7,35; 8,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,64</t>
+          <t>7,67; 8,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,71</t>
+          <t>6,93; 7,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,19</t>
+          <t>7,39; 8,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,85</t>
+          <t>6,91; 7,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,46</t>
+          <t>6,93; 7,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,13</t>
+          <t>7,49; 8,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,08</t>
+          <t>7,41; 8,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Clase-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,45</t>
+          <t>6,21; 7,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 8,97</t>
+          <t>6,94; 8,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,24</t>
+          <t>6,91; 8,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,86</t>
+          <t>6,54; 7,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,56</t>
+          <t>7,16; 8,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,77</t>
+          <t>6,72; 7,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,5</t>
+          <t>6,51; 7,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 8,38</t>
+          <t>7,21; 8,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,82</t>
+          <t>6,94; 7,79</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,8</t>
+          <t>4,94; 6,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,38</t>
+          <t>6,42; 8,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 9,99</t>
+          <t>7,37; 10,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,07</t>
+          <t>6,5; 8,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,9</t>
+          <t>6,15; 7,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 9,19</t>
+          <t>6,77; 9,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,41</t>
+          <t>6,14; 7,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,78</t>
+          <t>6,45; 7,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 9,11</t>
+          <t>7,3; 9,02</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,36</t>
+          <t>7,12; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,37</t>
+          <t>6,53; 8,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,82</t>
+          <t>6,38; 9,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 9,72</t>
+          <t>6,58; 9,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 8,61</t>
+          <t>6,7; 8,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,77</t>
+          <t>5,34; 7,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 9,11</t>
+          <t>7,1; 8,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 8,15</t>
+          <t>6,89; 8,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,56</t>
+          <t>6,37; 8,52</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,99</t>
+          <t>6,33; 8,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,23</t>
+          <t>7,04; 8,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 9,23</t>
+          <t>7,58; 9,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 7,66</t>
+          <t>6,64; 7,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,92</t>
+          <t>7,23; 8,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,67</t>
+          <t>6,29; 7,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 7,71</t>
+          <t>6,6; 7,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,26</t>
+          <t>7,26; 8,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,37</t>
+          <t>7,15; 8,33</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,64</t>
+          <t>6,14; 8,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,02</t>
+          <t>6,54; 7,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1132,32 +1132,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,71</t>
+          <t>5,2; 7,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,81</t>
+          <t>7,4; 9,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,68</t>
+          <t>6,46; 11,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,65</t>
+          <t>5,99; 7,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,54</t>
+          <t>7,16; 8,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,63</t>
+          <t>7,41; 10,57</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,11</t>
+          <t>6,36; 9,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,27; 17,24</t>
+          <t>8,31; 17,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,03</t>
+          <t>6,27; 9,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,15</t>
+          <t>7,49; 9,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,6</t>
+          <t>7,38; 8,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,28; 7,87</t>
+          <t>6,27; 7,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 9,15</t>
+          <t>7,18; 8,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,87</t>
+          <t>8,1; 13,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,59; 8,26</t>
+          <t>6,54; 8,34</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,55</t>
+          <t>6,71; 7,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,56</t>
+          <t>7,36; 8,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 8,62</t>
+          <t>7,69; 8,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,7</t>
+          <t>6,91; 7,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,2</t>
+          <t>7,38; 8,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,88</t>
+          <t>6,93; 7,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,49</t>
+          <t>6,91; 7,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 8,19</t>
+          <t>7,5; 8,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,11</t>
+          <t>7,41; 8,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3004_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3004_MoAR-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,72</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7,78</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,07</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,72</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,17</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,59</t>
+          <t>6,52; 7,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,85</t>
+          <t>7,09; 8,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,24</t>
+          <t>6,66; 7,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,93</t>
+          <t>6,13; 7,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,45</t>
+          <t>7,05; 8,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 7,8</t>
+          <t>6,86; 8,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,5</t>
+          <t>6,53; 7,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,3</t>
+          <t>7,22; 8,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,79</t>
+          <t>6,95; 7,81</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,82</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,77</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,24</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,29</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,82</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,77</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,77</t>
+          <t>6,47; 8,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 8,48</t>
+          <t>6,14; 7,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,14</t>
+          <t>6,74; 9,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,01</t>
+          <t>4,98; 6,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,84</t>
+          <t>6,47; 8,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,11</t>
+          <t>7,38; 10,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,38</t>
+          <t>6,17; 7,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,72</t>
+          <t>6,47; 7,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 9,02</t>
+          <t>7,28; 9,1</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,54</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,56</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,28</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,82</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,72</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,31</t>
+          <t>6,51; 9,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,31</t>
+          <t>6,78; 8,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,67</t>
+          <t>5,19; 7,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 9,72</t>
+          <t>7,16; 9,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,67</t>
+          <t>6,56; 8,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,73</t>
+          <t>6,47; 9,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,88</t>
+          <t>7,07; 9,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 8,12</t>
+          <t>6,88; 8,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,52</t>
+          <t>6,32; 8,52</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,95</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,97</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,97</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 8,05</t>
+          <t>6,65; 7,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 8,22</t>
+          <t>7,25; 8,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 9,3</t>
+          <t>6,34; 7,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,69</t>
+          <t>6,25; 8,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,82</t>
+          <t>7,03; 8,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,64</t>
+          <t>7,54; 9,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,64</t>
+          <t>6,64; 7,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,29</t>
+          <t>7,3; 8,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,33</t>
+          <t>7,17; 8,31</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,33</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,03</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,03</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,13</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>8,94</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,58</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,33</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 8,7</t>
+          <t>5,1; 7,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,98</t>
+          <t>7,48; 9,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 9,93</t>
+          <t>6,49; 11,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 7,76</t>
+          <t>6,11; 8,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,76</t>
+          <t>6,55; 8,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,49</t>
+          <t>8,05; 9,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 7,59</t>
+          <t>6,0; 7,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,52</t>
+          <t>7,16; 8,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,57</t>
+          <t>7,32; 10,48</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8,29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8,01</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7,02</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>7,4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>11,2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7,38</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8,29</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,01</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,14</t>
+          <t>7,54; 9,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 17,41</t>
+          <t>7,41; 8,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,04</t>
+          <t>6,33; 7,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,79</t>
+          <t>6,41; 9,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,61</t>
+          <t>8,29; 18,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,9</t>
+          <t>6,21; 9,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,97</t>
+          <t>7,21; 9,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,1; 13,94</t>
+          <t>8,11; 14,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,34</t>
+          <t>6,57; 8,4</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,76</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,08</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>8,11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,53</t>
+          <t>6,92; 7,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,51</t>
+          <t>7,41; 8,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 8,64</t>
+          <t>6,9; 7,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,66</t>
+          <t>6,7; 7,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,15</t>
+          <t>7,35; 8,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,95</t>
+          <t>7,68; 8,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,47</t>
+          <t>6,91; 7,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,19</t>
+          <t>7,5; 8,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,1</t>
+          <t>7,39; 8,08</t>
         </is>
       </c>
     </row>
